--- a/Config/GameConfig/Datas/__enums__.xlsx
+++ b/Config/GameConfig/Datas/__enums__.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Configs\GameConfig\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Config\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{670FBC43-0447-45CC-A930-C943579C10E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E94C13-D739-4038-A348-0E81E3ADCC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="108">
   <si>
     <t>##var</t>
   </si>
@@ -320,6 +320,98 @@
   </si>
   <si>
     <t>粪便</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>farm.ELandType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NORMAL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BLACK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RED</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WATER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SALT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑土地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红土地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄土地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水田地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>盐碱地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOCK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未解锁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Farmland</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ranchland</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fishland</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>农场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>牧场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>渔场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UNLOCKING</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>common.EModule</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -685,7 +777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -787,7 +879,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" s="3" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="C4" t="b">
         <v>0</v>
@@ -795,168 +887,152 @@
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" t="s">
-        <v>20</v>
+      <c r="H4" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>102</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
-      <c r="K4" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H5" s="3" t="s">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="J5">
         <v>2</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>35</v>
-      </c>
+      <c r="K5" s="3"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" t="s">
-        <v>23</v>
+      <c r="H6" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>104</v>
       </c>
       <c r="J6">
         <v>3</v>
       </c>
-      <c r="K6" t="s">
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="K8" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H12" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12">
+        <v>3</v>
+      </c>
+      <c r="K12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H7" t="s">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H13" t="s">
         <v>25</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I13" t="s">
         <v>26</v>
       </c>
-      <c r="J7">
+      <c r="J13">
         <v>4</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K13" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H8" s="3" t="s">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H14" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="J8">
+      <c r="J14">
         <v>5</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H9" t="s">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H15" t="s">
         <v>28</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I15" t="s">
         <v>29</v>
       </c>
-      <c r="J9">
+      <c r="J15">
         <v>6</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K15" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H12" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J12">
-        <v>2</v>
-      </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" t="b">
-        <v>1</v>
-      </c>
-      <c r="D14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H15" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J15">
-        <v>2</v>
-      </c>
-      <c r="K15" s="3"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B17" s="3" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="b">
         <v>1</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -964,191 +1040,353 @@
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H18" s="3" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="J18">
         <v>2</v>
       </c>
       <c r="K18" s="3"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H19" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="J19">
-        <v>3</v>
-      </c>
-    </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" t="b">
+        <v>1</v>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
       <c r="H20" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="J20">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H21" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="J21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K21" s="3"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H22" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="J22">
-        <v>6</v>
-      </c>
-    </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B23" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
       <c r="H23" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="J23">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H24" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="J24">
-        <v>8</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K24" s="3"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H25" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="J25">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H26" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="J26">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H27" t="s">
-        <v>59</v>
+      <c r="H27" s="3" t="s">
+        <v>53</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="J27">
-        <v>11</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="K27" s="3"/>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H28" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="J28">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H29" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="J29">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H30" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="J30">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H31" t="s">
-        <v>65</v>
+      <c r="H31" s="3" t="s">
+        <v>57</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="J31">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H32" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H33" t="s">
+        <v>59</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J33">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H34" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="J34">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H35" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J35">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H36" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J36">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H37" t="s">
+        <v>65</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="J37">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H38" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="I32" s="3" t="s">
+      <c r="I38" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="J32">
+      <c r="J38">
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H33" s="3" t="s">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H39" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="I33" s="3" t="s">
+      <c r="I39" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="J33">
+      <c r="J39">
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H34" t="s">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H40" t="s">
         <v>63</v>
       </c>
-      <c r="I34" s="3" t="s">
+      <c r="I40" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="J34">
+      <c r="J40">
         <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B42" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C42" t="b">
+        <v>0</v>
+      </c>
+      <c r="D42" t="b">
+        <v>1</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B43" s="3"/>
+      <c r="H43" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H44" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H45" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H46" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="J46">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H47" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="J47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H48" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J48">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="8:10" x14ac:dyDescent="0.2">
+      <c r="H49" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J49">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Config/GameConfig/Datas/__enums__.xlsx
+++ b/Config/GameConfig/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Config\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E94C13-D739-4038-A348-0E81E3ADCC21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D9397C-EFA0-4599-95E2-DDC46F583AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="61">
   <si>
     <t>##var</t>
   </si>
@@ -79,70 +79,6 @@
     <t>注释</t>
   </si>
   <si>
-    <t>WHITE</t>
-  </si>
-  <si>
-    <t>白</t>
-  </si>
-  <si>
-    <t>最差品质</t>
-  </si>
-  <si>
-    <t>BLUE</t>
-  </si>
-  <si>
-    <t>蓝</t>
-  </si>
-  <si>
-    <t>蓝色的</t>
-  </si>
-  <si>
-    <t>PURPLE</t>
-  </si>
-  <si>
-    <t>紫</t>
-  </si>
-  <si>
-    <t>紫色的</t>
-  </si>
-  <si>
-    <t>RED</t>
-  </si>
-  <si>
-    <t>红</t>
-  </si>
-  <si>
-    <t>最高品质</t>
-  </si>
-  <si>
-    <t>绿</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GREEN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>YELLOW</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>绿色</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄色</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item.EQuality</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>item.EFornitureType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -163,26 +99,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>item.ECropsType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SEED</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CROP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>种子</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>收成物</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>item.ETag</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -320,98 +236,6 @@
   </si>
   <si>
     <t>粪便</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>farm.ELandType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NORMAL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BLACK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RED</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WATER</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SALT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>普通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黑土地</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>红土地</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黄土地</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>水田地</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>盐碱地</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LOCK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>未解锁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Farmland</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ranchland</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Fishland</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>农场</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>牧场</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>渔场</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UNLOCKING</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>解锁中</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>common.EModule</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -777,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -878,47 +702,18 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B4" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
+      <c r="B4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H5" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
       <c r="K5" s="3"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H6" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H8" s="3"/>
@@ -926,101 +721,21 @@
       <c r="K8" s="3"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" t="s">
-        <v>19</v>
-      </c>
-      <c r="I10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="K10" t="s">
-        <v>21</v>
-      </c>
+      <c r="B10" s="3"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11">
-        <v>2</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H12" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" t="s">
-        <v>23</v>
-      </c>
-      <c r="J12">
-        <v>3</v>
-      </c>
-      <c r="K12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H13" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" t="s">
-        <v>26</v>
-      </c>
-      <c r="J13">
-        <v>4</v>
-      </c>
-      <c r="K13" t="s">
-        <v>27</v>
-      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="K11" s="3"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H14" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J14">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H15" t="s">
-        <v>28</v>
-      </c>
-      <c r="I15" t="s">
-        <v>29</v>
-      </c>
-      <c r="J15">
-        <v>6</v>
-      </c>
-      <c r="K15" t="s">
-        <v>30</v>
-      </c>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="K14" s="3"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B17" s="3" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="C17" t="b">
         <v>0</v>
@@ -1029,10 +744,10 @@
         <v>1</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1040,10 +755,10 @@
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H18" s="3" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="J18">
         <v>2</v>
@@ -1051,40 +766,18 @@
       <c r="K18" s="3"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B20" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" t="b">
-        <v>1</v>
-      </c>
-      <c r="D20" t="b">
-        <v>1</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="J20">
-        <v>1</v>
-      </c>
+      <c r="B20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H21" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J21">
-        <v>2</v>
-      </c>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
       <c r="K21" s="3"/>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B23" s="3" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="C23" t="b">
         <v>1</v>
@@ -1093,10 +786,10 @@
         <v>1</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -1104,10 +797,10 @@
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H24" s="3" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="J24">
         <v>2</v>
@@ -1116,10 +809,10 @@
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H25" s="3" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="J25">
         <v>3</v>
@@ -1127,10 +820,10 @@
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H26" s="3" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="J26">
         <v>4</v>
@@ -1138,10 +831,10 @@
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H27" s="3" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="J27">
         <v>5</v>
@@ -1150,10 +843,10 @@
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H28" s="3" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="J28">
         <v>6</v>
@@ -1161,10 +854,10 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H29" s="3" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="J29">
         <v>7</v>
@@ -1172,10 +865,10 @@
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H30" s="3" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="J30">
         <v>8</v>
@@ -1183,10 +876,10 @@
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H31" s="3" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="J31">
         <v>9</v>
@@ -1194,10 +887,10 @@
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H32" s="3" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="J32">
         <v>10</v>
@@ -1205,10 +898,10 @@
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H33" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="J33">
         <v>11</v>
@@ -1216,10 +909,10 @@
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H34" s="3" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="J34">
         <v>12</v>
@@ -1227,10 +920,10 @@
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H35" s="3" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="J35">
         <v>13</v>
@@ -1238,10 +931,10 @@
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H36" s="3" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="J36">
         <v>14</v>
@@ -1249,10 +942,10 @@
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H37" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="J37">
         <v>15</v>
@@ -1260,10 +953,10 @@
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H38" s="3" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="J38">
         <v>16</v>
@@ -1271,10 +964,10 @@
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H39" s="3" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="J39">
         <v>17</v>
@@ -1282,112 +975,87 @@
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H40" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="J40">
         <v>18</v>
       </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B42" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C42" t="b">
-        <v>0</v>
-      </c>
-      <c r="D42" t="b">
-        <v>1</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
+      <c r="B42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B43" s="3"/>
-      <c r="H43" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="J43">
-        <v>1</v>
-      </c>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H44" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="J44">
-        <v>2</v>
-      </c>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H45" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="J45">
-        <v>3</v>
-      </c>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H46" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J46">
-        <v>4</v>
-      </c>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H47" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="J47">
-        <v>5</v>
-      </c>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H48" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="J48">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="8:10" x14ac:dyDescent="0.2">
-      <c r="H49" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J49">
-        <v>7</v>
-      </c>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="H51" s="3"/>
+      <c r="I51" s="3"/>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="H52" s="3"/>
+      <c r="I52" s="3"/>
+    </row>
+    <row r="54" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+    </row>
+    <row r="55" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I55" s="3"/>
+    </row>
+    <row r="56" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I56" s="3"/>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I57" s="3"/>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I58" s="3"/>
+    </row>
+    <row r="59" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I59" s="3"/>
+    </row>
+    <row r="60" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I60" s="3"/>
+    </row>
+    <row r="61" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="H61" s="3"/>
+      <c r="I61" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
